--- a/data/trans_dic/IP19C03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por empastes</t>
+          <t>Menores que en su última visita al dentista fue por empastes (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 74,5</t>
+          <t>14,91; 73,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 49,43</t>
+          <t>7,06; 46,45</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 17,74</t>
+          <t>6,69; 18,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,13; 15,71</t>
+          <t>4,97; 16,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,31; 23,63</t>
+          <t>8,99; 23,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,51; 26,57</t>
+          <t>11,62; 26,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 14,89</t>
+          <t>4,7; 14,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,56; 21,82</t>
+          <t>8,58; 21,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,26; 20,8</t>
+          <t>8,53; 21,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,87; 27,65</t>
+          <t>12,26; 26,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 14,58</t>
+          <t>6,93; 14,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 16,48</t>
+          <t>7,96; 16,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,31; 19,91</t>
+          <t>10,36; 19,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,56; 24,45</t>
+          <t>13,4; 24,0</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,11; 27,03</t>
+          <t>13,75; 26,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,09; 27,03</t>
+          <t>15,16; 27,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,69; 20,34</t>
+          <t>10,79; 20,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,07; 28,97</t>
+          <t>14,95; 30,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,47; 23,12</t>
+          <t>11,49; 23,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,2; 25,39</t>
+          <t>14,41; 25,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,06; 21,79</t>
+          <t>11,72; 21,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,8; 23,62</t>
+          <t>11,73; 23,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,28; 22,83</t>
+          <t>13,9; 22,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,27; 24,26</t>
+          <t>16,45; 24,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,35; 19,51</t>
+          <t>12,74; 19,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,72; 23,63</t>
+          <t>14,12; 23,42</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,37; 32,6</t>
+          <t>21,26; 32,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,63; 33,44</t>
+          <t>20,92; 32,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,41; 25,62</t>
+          <t>14,74; 25,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,24; 19,61</t>
+          <t>10,95; 19,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 27,37</t>
+          <t>17,27; 27,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,59; 29,19</t>
+          <t>18,44; 29,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,3; 28,94</t>
+          <t>16,85; 29,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 20,47</t>
+          <t>10,92; 20,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,71; 28,26</t>
+          <t>20,36; 28,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,02; 29,57</t>
+          <t>21,07; 29,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,88; 25,88</t>
+          <t>17,5; 25,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,1; 18,65</t>
+          <t>12,4; 18,75</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,27; 24,45</t>
+          <t>17,59; 24,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,58; 24,13</t>
+          <t>17,28; 24,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 20,23</t>
+          <t>13,99; 20,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,61; 21,23</t>
+          <t>14,41; 21,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,63</t>
+          <t>14,43; 21,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,99; 22,91</t>
+          <t>15,88; 22,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,31; 21,83</t>
+          <t>14,87; 21,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,8</t>
+          <t>13,49; 19,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,81; 21,81</t>
+          <t>16,96; 21,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,74; 22,31</t>
+          <t>17,62; 22,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,38; 19,96</t>
+          <t>15,58; 20,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,82; 19,27</t>
+          <t>14,4; 19,4</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por empastes (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2422</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2422</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>864; 4271</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>785; 5163</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>9703</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7162</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10485</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12009</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7270</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12694</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11366</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>14172</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>16973</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>21850</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>26181</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5645; 15263</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3863; 12481</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6118; 16315</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7693; 17594</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3779; 11984</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7895; 19808</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7008; 17507</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>9458; 20769</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>11421; 23824</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>13516; 27238</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>15555; 29756</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>19213; 34398</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>19547</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26257</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22358</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24713</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17652</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25560</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24391</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>28221</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>37199</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>51816</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>46750</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>52934</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>13640; 26521</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18872; 33943</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16068; 30690</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18221; 36738</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12151; 25143</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>19040; 33746</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17502; 32467</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>19334; 39382</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>28491; 45565</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>42190; 63066</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>38004; 58086</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>40475; 67151</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>43539</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>39525</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>28788</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29762</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38549</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>32866</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>31333</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>36395</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>82088</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>60121</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>66158</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>34751; 53266</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30944; 48574</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>21386; 36647</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>21643; 38248</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>29990; 48414</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>26135; 42084</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>22913; 39887</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>25905; 48226</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>68653; 94837</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>61046; 84299</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>49190; 71570</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>53915; 81545</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>72789</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>72944</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>61631</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>68906</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>63471</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>71120</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67090</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>78788</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>136260</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>144064</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128721</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>147694</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>61716; 87218</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>61062; 85384</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>50723; 73943</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>56430; 84026</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>52195; 76163</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>58221; 83474</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>54839; 79158</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>65330; 96364</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>120886; 152067</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>126829; 162877</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>113958; 147795</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>126168; 169935</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Edad-trans_dic.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 73,68</t>
+          <t>14,03; 74,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 46,45</t>
+          <t>6,96; 50,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,69; 18,1</t>
+          <t>7,12; 18,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 16,07</t>
+          <t>4,71; 15,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,99; 23,97</t>
+          <t>9,58; 24,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,62; 26,58</t>
+          <t>11,0; 26,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 14,9</t>
+          <t>5,01; 14,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 21,52</t>
+          <t>8,54; 21,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 21,32</t>
+          <t>8,37; 20,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,26; 26,93</t>
+          <t>11,43; 27,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 14,46</t>
+          <t>6,75; 14,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 16,05</t>
+          <t>7,84; 16,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,36; 19,81</t>
+          <t>10,2; 19,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,4; 24,0</t>
+          <t>13,19; 23,65</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,75; 26,74</t>
+          <t>14,06; 26,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,16; 27,27</t>
+          <t>15,12; 27,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,79; 20,61</t>
+          <t>10,35; 19,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,95; 30,14</t>
+          <t>13,99; 29,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,49; 23,78</t>
+          <t>11,4; 22,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,41; 25,55</t>
+          <t>14,43; 25,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 21,74</t>
+          <t>11,75; 21,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,73; 23,9</t>
+          <t>12,0; 23,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,9; 22,24</t>
+          <t>14,14; 22,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,45; 24,58</t>
+          <t>16,31; 24,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,74; 19,47</t>
+          <t>12,46; 19,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,12; 23,42</t>
+          <t>13,93; 22,99</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,26; 32,58</t>
+          <t>21,42; 33,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,92; 32,84</t>
+          <t>21,35; 32,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,74; 25,26</t>
+          <t>14,88; 25,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,95; 19,34</t>
+          <t>11,21; 19,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,27; 27,87</t>
+          <t>17,24; 27,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,44; 29,69</t>
+          <t>17,66; 29,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,85; 29,33</t>
+          <t>17,29; 29,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,92; 20,33</t>
+          <t>11,29; 20,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,36; 28,13</t>
+          <t>20,57; 28,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,07; 29,1</t>
+          <t>21,01; 29,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,5; 25,46</t>
+          <t>17,62; 25,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,4; 18,75</t>
+          <t>12,21; 18,63</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,59; 24,85</t>
+          <t>17,8; 24,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,28; 24,16</t>
+          <t>17,13; 24,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,99; 20,39</t>
+          <t>14,16; 20,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,41; 21,46</t>
+          <t>14,03; 21,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,43; 21,06</t>
+          <t>14,62; 20,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,88; 22,77</t>
+          <t>16,33; 22,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,87; 21,47</t>
+          <t>15,14; 21,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,89</t>
+          <t>13,07; 19,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,96; 21,34</t>
+          <t>16,79; 21,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,62; 22,62</t>
+          <t>17,47; 22,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,58; 20,21</t>
+          <t>15,39; 19,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,4; 19,4</t>
+          <t>14,79; 19,38</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>864; 4271</t>
+          <t>813; 4334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>785; 5163</t>
+          <t>773; 5652</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5645; 15263</t>
+          <t>6007; 15636</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3863; 12481</t>
+          <t>3660; 12155</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6118; 16315</t>
+          <t>6522; 16510</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7693; 17594</t>
+          <t>7281; 17224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3779; 11984</t>
+          <t>4030; 11950</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7895; 19808</t>
+          <t>7865; 19519</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7008; 17507</t>
+          <t>6878; 17031</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9458; 20769</t>
+          <t>8814; 21465</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11421; 23824</t>
+          <t>11125; 23158</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13516; 27238</t>
+          <t>13317; 27304</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15555; 29756</t>
+          <t>15313; 29540</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19213; 34398</t>
+          <t>18902; 33895</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13640; 26521</t>
+          <t>13945; 25992</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18872; 33943</t>
+          <t>18815; 34443</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16068; 30690</t>
+          <t>15406; 29752</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18221; 36738</t>
+          <t>17056; 35893</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12151; 25143</t>
+          <t>12048; 24281</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19040; 33746</t>
+          <t>19054; 33850</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17502; 32467</t>
+          <t>17553; 32589</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19334; 39382</t>
+          <t>19781; 39138</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28491; 45565</t>
+          <t>28967; 46774</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42190; 63066</t>
+          <t>41850; 61895</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38004; 58086</t>
+          <t>37158; 59121</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40475; 67151</t>
+          <t>39942; 65912</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34751; 53266</t>
+          <t>35023; 54293</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30944; 48574</t>
+          <t>31584; 48769</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21386; 36647</t>
+          <t>21586; 36508</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21643; 38248</t>
+          <t>22169; 38728</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29990; 48414</t>
+          <t>29954; 48416</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26135; 42084</t>
+          <t>25034; 41954</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22913; 39887</t>
+          <t>23509; 40255</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25905; 48226</t>
+          <t>26786; 49397</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68653; 94837</t>
+          <t>69361; 95925</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>61046; 84299</t>
+          <t>60858; 84419</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49190; 71570</t>
+          <t>49535; 71716</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53915; 81545</t>
+          <t>53098; 81050</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61716; 87218</t>
+          <t>62455; 85858</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>61062; 85384</t>
+          <t>60546; 84849</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50723; 73943</t>
+          <t>51337; 73260</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56430; 84026</t>
+          <t>54937; 82922</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>52195; 76163</t>
+          <t>52878; 75264</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58221; 83474</t>
+          <t>59864; 83812</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54839; 79158</t>
+          <t>55840; 81047</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>65330; 96364</t>
+          <t>63316; 94934</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>120886; 152067</t>
+          <t>119633; 152819</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>126829; 162877</t>
+          <t>125795; 161024</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>113958; 147795</t>
+          <t>112577; 145356</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>126168; 169935</t>
+          <t>129528; 169743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,27 +684,27 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>37,25%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,03; 74,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>12,03; 71,53</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 50,86</t>
+          <t>6,48; 49,0</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>11,51%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,22%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>15,4%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 18,54</t>
+          <t>4,81; 14,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,71; 15,65</t>
+          <t>8,56; 21,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 24,26</t>
+          <t>8,26; 20,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,0; 26,02</t>
+          <t>12,7; 29,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 14,86</t>
+          <t>6,45; 17,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 21,2</t>
+          <t>5,13; 15,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,37; 20,74</t>
+          <t>9,31; 23,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,43; 27,83</t>
+          <t>12,04; 27,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 14,06</t>
+          <t>7,13; 14,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 16,08</t>
+          <t>8,24; 16,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 19,67</t>
+          <t>10,31; 19,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,19; 23,65</t>
+          <t>14,13; 25,87</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,35%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19,71%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>21,1%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>15,01%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,27%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,06; 26,2</t>
+          <t>11,47; 23,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,12; 27,68</t>
+          <t>14,2; 25,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,35; 19,98</t>
+          <t>12,06; 21,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,99; 29,44</t>
+          <t>10,94; 22,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,4; 22,97</t>
+          <t>14,11; 27,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,43; 25,63</t>
+          <t>15,09; 27,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,75; 21,82</t>
+          <t>10,69; 20,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,0; 23,75</t>
+          <t>12,98; 24,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,14; 22,83</t>
+          <t>14,28; 22,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,31; 24,13</t>
+          <t>16,27; 24,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,46; 19,82</t>
+          <t>12,35; 19,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,93; 22,99</t>
+          <t>13,86; 21,76</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23,19%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23,04%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>26,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>26,72%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>19,84%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,04%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,42; 33,21</t>
+          <t>17,46; 27,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,35; 32,97</t>
+          <t>17,59; 29,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,88; 25,16</t>
+          <t>17,3; 28,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,21; 19,59</t>
+          <t>10,85; 20,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,24; 27,87</t>
+          <t>21,37; 32,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,66; 29,6</t>
+          <t>21,63; 33,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,29; 29,6</t>
+          <t>14,41; 25,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 20,82</t>
+          <t>10,94; 19,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,57; 28,45</t>
+          <t>20,71; 28,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,01; 29,14</t>
+          <t>21,02; 29,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,62; 25,51</t>
+          <t>17,88; 25,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,21; 18,63</t>
+          <t>11,9; 18,25</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>20,74%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20,64%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,8; 24,47</t>
+          <t>14,55; 20,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 24,01</t>
+          <t>15,99; 22,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,16; 20,2</t>
+          <t>15,31; 21,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,03; 21,17</t>
+          <t>12,59; 19,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,62; 20,81</t>
+          <t>17,27; 24,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,33; 22,86</t>
+          <t>17,58; 24,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,14; 21,98</t>
+          <t>13,77; 20,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,07; 19,6</t>
+          <t>14,04; 20,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,79; 21,44</t>
+          <t>16,81; 21,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 22,37</t>
+          <t>17,74; 22,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,39; 19,87</t>
+          <t>15,38; 19,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,79; 19,38</t>
+          <t>14,34; 18,67</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,27 +1612,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>2262</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2262</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>813; 4334</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1680,27 +1680,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>731; 4343</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>773; 5652</t>
+          <t>697; 5267</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7270</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12694</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11366</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13212</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9703</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7162</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10485</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12009</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7270</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12694</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11366</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26181</t>
+          <t>25324</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6007; 15636</t>
+          <t>3870; 11976</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3660; 12155</t>
+          <t>7882; 20085</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6522; 16510</t>
+          <t>6784; 17085</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7281; 17224</t>
+          <t>8580; 19723</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4030; 11950</t>
+          <t>5438; 14965</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7865; 19519</t>
+          <t>3988; 12202</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6878; 17031</t>
+          <t>6334; 16081</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8814; 21465</t>
+          <t>7641; 17698</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11125; 23158</t>
+          <t>11739; 24022</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13317; 27304</t>
+          <t>13993; 27976</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15313; 29540</t>
+          <t>15486; 29898</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18902; 33895</t>
+          <t>18508; 33901</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17652</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25560</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24391</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24914</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>19547</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>26257</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>22358</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24713</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>17652</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25560</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>24391</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28221</t>
+          <t>22476</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52934</t>
+          <t>47390</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13945; 25992</t>
+          <t>12128; 24445</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18815; 34443</t>
+          <t>18762; 33534</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15406; 29752</t>
+          <t>18015; 32541</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17056; 35893</t>
+          <t>16986; 34325</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12048; 24281</t>
+          <t>13993; 26809</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19054; 33850</t>
+          <t>18774; 33641</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17553; 32589</t>
+          <t>15914; 30294</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19781; 39138</t>
+          <t>15811; 30331</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28967; 46774</t>
+          <t>29260; 46776</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41850; 61895</t>
+          <t>41743; 62226</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37158; 59121</t>
+          <t>36844; 58195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39942; 65912</t>
+          <t>38410; 60307</t>
         </is>
       </c>
     </row>
@@ -2133,37 +2133,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38549</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>32866</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31333</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34745</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>43539</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>39525</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>28788</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29762</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>38549</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>32866</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>31333</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>30461</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66158</t>
+          <t>65206</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35023; 54293</t>
+          <t>30329; 47545</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31584; 48769</t>
+          <t>24941; 41382</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21586; 36508</t>
+          <t>23530; 39366</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22169; 38728</t>
+          <t>25348; 46847</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29954; 48416</t>
+          <t>34942; 53299</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25034; 41954</t>
+          <t>31989; 49459</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23509; 40255</t>
+          <t>20904; 37181</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26786; 49397</t>
+          <t>22417; 39460</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69361; 95925</t>
+          <t>69839; 95299</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60858; 84419</t>
+          <t>60885; 85652</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49535; 71716</t>
+          <t>50265; 72750</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53098; 81050</t>
+          <t>52163; 80036</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>97</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>63471</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>71120</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>67090</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>72870</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>72789</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>72944</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>61631</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>68906</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>63471</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>71120</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67090</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>78788</t>
+          <t>67312</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>147694</t>
+          <t>140182</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>62455; 85858</t>
+          <t>52631; 74619</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>60546; 84849</t>
+          <t>58627; 83973</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51337; 73260</t>
+          <t>56471; 80516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54937; 82922</t>
+          <t>58072; 88226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>52878; 75264</t>
+          <t>60600; 85800</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>59864; 83812</t>
+          <t>62117; 85259</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55840; 81047</t>
+          <t>49923; 73348</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>63316; 94934</t>
+          <t>55645; 79711</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>119633; 152819</t>
+          <t>119807; 155465</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>125795; 161024</t>
+          <t>127695; 160607</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112577; 145356</t>
+          <t>112503; 146019</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>129528; 169743</t>
+          <t>122944; 160070</t>
         </is>
       </c>
     </row>
